--- a/public/Plantilla_Carga_Masiva_Turnos_SERGEM.xlsx
+++ b/public/Plantilla_Carga_Masiva_Turnos_SERGEM.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AT3"/>
+  <dimension ref="A1:BA3"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="26.83203125" customWidth="1"/>
@@ -409,43 +409,50 @@
     <col min="7" max="7" width="9.83203125" customWidth="1"/>
     <col min="8" max="8" width="9.83203125" customWidth="1"/>
     <col min="9" max="9" width="9.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" customWidth="1"/>
-    <col min="12" max="12" width="9.83203125" customWidth="1"/>
+    <col min="10" max="10" width="28.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="24.83203125" customWidth="1"/>
     <col min="13" max="13" width="9.83203125" customWidth="1"/>
     <col min="14" max="14" width="9.83203125" customWidth="1"/>
     <col min="15" max="15" width="9.83203125" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="17" max="17" width="24.83203125" customWidth="1"/>
-    <col min="18" max="18" width="9.83203125" customWidth="1"/>
-    <col min="19" max="19" width="9.83203125" customWidth="1"/>
+    <col min="16" max="16" width="9.83203125" customWidth="1"/>
+    <col min="17" max="17" width="28.83203125" customWidth="1"/>
+    <col min="18" max="18" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="24.83203125" customWidth="1"/>
     <col min="20" max="20" width="9.83203125" customWidth="1"/>
     <col min="21" max="21" width="9.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" customWidth="1"/>
-    <col min="23" max="23" width="24.83203125" customWidth="1"/>
-    <col min="24" max="24" width="9.83203125" customWidth="1"/>
-    <col min="25" max="25" width="9.83203125" customWidth="1"/>
-    <col min="26" max="26" width="9.83203125" customWidth="1"/>
+    <col min="22" max="22" width="9.83203125" customWidth="1"/>
+    <col min="23" max="23" width="9.83203125" customWidth="1"/>
+    <col min="24" max="24" width="28.83203125" customWidth="1"/>
+    <col min="25" max="25" width="12.83203125" customWidth="1"/>
+    <col min="26" max="26" width="24.83203125" customWidth="1"/>
     <col min="27" max="27" width="9.83203125" customWidth="1"/>
-    <col min="28" max="28" width="12.83203125" customWidth="1"/>
-    <col min="29" max="29" width="24.83203125" customWidth="1"/>
+    <col min="28" max="28" width="9.83203125" customWidth="1"/>
+    <col min="29" max="29" width="9.83203125" customWidth="1"/>
     <col min="30" max="30" width="9.83203125" customWidth="1"/>
-    <col min="31" max="31" width="9.83203125" customWidth="1"/>
-    <col min="32" max="32" width="9.83203125" customWidth="1"/>
-    <col min="33" max="33" width="9.83203125" customWidth="1"/>
-    <col min="34" max="34" width="12.83203125" customWidth="1"/>
-    <col min="35" max="35" width="24.83203125" customWidth="1"/>
+    <col min="31" max="31" width="28.83203125" customWidth="1"/>
+    <col min="32" max="32" width="12.83203125" customWidth="1"/>
+    <col min="33" max="33" width="24.83203125" customWidth="1"/>
+    <col min="34" max="34" width="9.83203125" customWidth="1"/>
+    <col min="35" max="35" width="9.83203125" customWidth="1"/>
     <col min="36" max="36" width="9.83203125" customWidth="1"/>
     <col min="37" max="37" width="9.83203125" customWidth="1"/>
-    <col min="38" max="38" width="9.83203125" customWidth="1"/>
-    <col min="39" max="39" width="9.83203125" customWidth="1"/>
-    <col min="40" max="40" width="12.83203125" customWidth="1"/>
-    <col min="41" max="41" width="24.83203125" customWidth="1"/>
+    <col min="38" max="38" width="28.83203125" customWidth="1"/>
+    <col min="39" max="39" width="12.83203125" customWidth="1"/>
+    <col min="40" max="40" width="24.83203125" customWidth="1"/>
+    <col min="41" max="41" width="9.83203125" customWidth="1"/>
     <col min="42" max="42" width="9.83203125" customWidth="1"/>
     <col min="43" max="43" width="9.83203125" customWidth="1"/>
     <col min="44" max="44" width="9.83203125" customWidth="1"/>
-    <col min="45" max="45" width="9.83203125" customWidth="1"/>
-    <col min="46" max="46" width="30.83203125" customWidth="1"/>
+    <col min="45" max="45" width="28.83203125" customWidth="1"/>
+    <col min="46" max="46" width="12.83203125" customWidth="1"/>
+    <col min="47" max="47" width="24.83203125" customWidth="1"/>
+    <col min="48" max="48" width="9.83203125" customWidth="1"/>
+    <col min="49" max="49" width="9.83203125" customWidth="1"/>
+    <col min="50" max="50" width="9.83203125" customWidth="1"/>
+    <col min="51" max="51" width="9.83203125" customWidth="1"/>
+    <col min="52" max="52" width="28.83203125" customWidth="1"/>
+    <col min="53" max="53" width="32.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,115 +484,136 @@
         <v>Lunes_Fin2</v>
       </c>
       <c r="J1" t="str">
+        <v>Lunes_Observaciones</v>
+      </c>
+      <c r="K1" t="str">
         <v>Martes_Tipo</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Martes_Cliente</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Martes_Inicio1</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>Martes_Fin1</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Martes_Inicio2</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Martes_Fin2</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
+        <v>Martes_Observaciones</v>
+      </c>
+      <c r="R1" t="str">
         <v>Miercoles_Tipo</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="S1" t="str">
         <v>Miercoles_Cliente</v>
       </c>
-      <c r="R1" t="str">
+      <c r="T1" t="str">
         <v>Miercoles_Inicio1</v>
       </c>
-      <c r="S1" t="str">
+      <c r="U1" t="str">
         <v>Miercoles_Fin1</v>
       </c>
-      <c r="T1" t="str">
+      <c r="V1" t="str">
         <v>Miercoles_Inicio2</v>
       </c>
-      <c r="U1" t="str">
+      <c r="W1" t="str">
         <v>Miercoles_Fin2</v>
       </c>
-      <c r="V1" t="str">
+      <c r="X1" t="str">
+        <v>Miercoles_Observaciones</v>
+      </c>
+      <c r="Y1" t="str">
         <v>Jueves_Tipo</v>
       </c>
-      <c r="W1" t="str">
+      <c r="Z1" t="str">
         <v>Jueves_Cliente</v>
       </c>
-      <c r="X1" t="str">
+      <c r="AA1" t="str">
         <v>Jueves_Inicio1</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="AB1" t="str">
         <v>Jueves_Fin1</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AC1" t="str">
         <v>Jueves_Inicio2</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AD1" t="str">
         <v>Jueves_Fin2</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AE1" t="str">
+        <v>Jueves_Observaciones</v>
+      </c>
+      <c r="AF1" t="str">
         <v>Viernes_Tipo</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AG1" t="str">
         <v>Viernes_Cliente</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AH1" t="str">
         <v>Viernes_Inicio1</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AI1" t="str">
         <v>Viernes_Fin1</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AJ1" t="str">
         <v>Viernes_Inicio2</v>
       </c>
-      <c r="AG1" t="str">
+      <c r="AK1" t="str">
         <v>Viernes_Fin2</v>
       </c>
-      <c r="AH1" t="str">
+      <c r="AL1" t="str">
+        <v>Viernes_Observaciones</v>
+      </c>
+      <c r="AM1" t="str">
         <v>Sabado_Tipo</v>
       </c>
-      <c r="AI1" t="str">
+      <c r="AN1" t="str">
         <v>Sabado_Cliente</v>
       </c>
-      <c r="AJ1" t="str">
+      <c r="AO1" t="str">
         <v>Sabado_Inicio1</v>
       </c>
-      <c r="AK1" t="str">
+      <c r="AP1" t="str">
         <v>Sabado_Fin1</v>
       </c>
-      <c r="AL1" t="str">
+      <c r="AQ1" t="str">
         <v>Sabado_Inicio2</v>
       </c>
-      <c r="AM1" t="str">
+      <c r="AR1" t="str">
         <v>Sabado_Fin2</v>
       </c>
-      <c r="AN1" t="str">
+      <c r="AS1" t="str">
+        <v>Sabado_Observaciones</v>
+      </c>
+      <c r="AT1" t="str">
         <v>Domingo_Tipo</v>
       </c>
-      <c r="AO1" t="str">
+      <c r="AU1" t="str">
         <v>Domingo_Cliente</v>
       </c>
-      <c r="AP1" t="str">
+      <c r="AV1" t="str">
         <v>Domingo_Inicio1</v>
       </c>
-      <c r="AQ1" t="str">
+      <c r="AW1" t="str">
         <v>Domingo_Fin1</v>
       </c>
-      <c r="AR1" t="str">
+      <c r="AX1" t="str">
         <v>Domingo_Inicio2</v>
       </c>
-      <c r="AS1" t="str">
+      <c r="AY1" t="str">
         <v>Domingo_Fin2</v>
       </c>
-      <c r="AT1" t="str">
-        <v>Observaciones</v>
+      <c r="AZ1" t="str">
+        <v>Domingo_Observaciones</v>
+      </c>
+      <c r="BA1" t="str">
+        <v>Observaciones_Generales</v>
       </c>
     </row>
     <row r="2">
@@ -593,7 +621,7 @@
         <v>1017123456</v>
       </c>
       <c r="B2" t="str">
-        <v>Juan Camilo Lopez</v>
+        <v>Juan Camilo López</v>
       </c>
       <c r="C2" t="str">
         <v>2026-08-03</v>
@@ -617,115 +645,136 @@
         <v/>
       </c>
       <c r="J2" t="str">
+        <v>Llegar 10 min antes en sede principal</v>
+      </c>
+      <c r="K2" t="str">
         <v>Partido</v>
       </c>
-      <c r="K2" t="str">
+      <c r="L2" t="str">
         <v>Almacenes Éxito S.A.</v>
       </c>
-      <c r="L2" t="str">
+      <c r="M2" t="str">
         <v>07:00</v>
       </c>
-      <c r="M2" t="str">
+      <c r="N2" t="str">
         <v>11:00</v>
       </c>
-      <c r="N2" t="str">
+      <c r="O2" t="str">
         <v>14:00</v>
       </c>
-      <c r="O2" t="str">
+      <c r="P2" t="str">
         <v>18:00</v>
       </c>
-      <c r="P2" t="str">
+      <c r="Q2" t="str">
+        <v>Ruta express norte y llevar datáfono</v>
+      </c>
+      <c r="R2" t="str">
         <v>Continua</v>
       </c>
-      <c r="Q2" t="str">
+      <c r="S2" t="str">
         <v>Droguerías Comfandi</v>
       </c>
-      <c r="R2" t="str">
+      <c r="T2" t="str">
         <v>07:00</v>
       </c>
-      <c r="S2" t="str">
+      <c r="U2" t="str">
         <v>15:00</v>
       </c>
-      <c r="T2" t="str">
-        <v/>
-      </c>
-      <c r="U2" t="str">
-        <v/>
-      </c>
       <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v>Verificar sellos de seguridad de paquetes</v>
+      </c>
+      <c r="Y2" t="str">
         <v>Partido</v>
       </c>
-      <c r="W2" t="str">
+      <c r="Z2" t="str">
         <v>Droguerías Comfandi</v>
       </c>
-      <c r="X2" t="str">
+      <c r="AA2" t="str">
         <v>07:00</v>
       </c>
-      <c r="Y2" t="str">
+      <c r="AB2" t="str">
         <v>11:00</v>
       </c>
-      <c r="Z2" t="str">
+      <c r="AC2" t="str">
         <v>14:00</v>
       </c>
-      <c r="AA2" t="str">
+      <c r="AD2" t="str">
         <v>18:00</v>
       </c>
-      <c r="AB2" t="str">
+      <c r="AE2" t="str">
+        <v>Priorizar entregas de farmacia</v>
+      </c>
+      <c r="AF2" t="str">
         <v>Continua</v>
       </c>
-      <c r="AC2" t="str">
+      <c r="AG2" t="str">
         <v>Almacenes Éxito S.A.</v>
       </c>
-      <c r="AD2" t="str">
+      <c r="AH2" t="str">
         <v>07:00</v>
       </c>
-      <c r="AE2" t="str">
+      <c r="AI2" t="str">
         <v>15:00</v>
       </c>
-      <c r="AF2" t="str">
-        <v/>
-      </c>
-      <c r="AG2" t="str">
-        <v/>
-      </c>
-      <c r="AH2" t="str">
+      <c r="AJ2" t="str">
+        <v/>
+      </c>
+      <c r="AK2" t="str">
+        <v/>
+      </c>
+      <c r="AL2" t="str">
+        <v>Revisar combustible antes de iniciar ruta</v>
+      </c>
+      <c r="AM2" t="str">
         <v>Continua</v>
       </c>
-      <c r="AI2" t="str">
+      <c r="AN2" t="str">
         <v>Almacenes Éxito S.A.</v>
       </c>
-      <c r="AJ2" t="str">
+      <c r="AO2" t="str">
         <v>08:00</v>
       </c>
-      <c r="AK2" t="str">
+      <c r="AP2" t="str">
         <v>13:00</v>
       </c>
-      <c r="AL2" t="str">
-        <v/>
-      </c>
-      <c r="AM2" t="str">
-        <v/>
-      </c>
-      <c r="AN2" t="str">
+      <c r="AQ2" t="str">
+        <v/>
+      </c>
+      <c r="AR2" t="str">
+        <v/>
+      </c>
+      <c r="AS2" t="str">
+        <v>Turno reforzado de fin de semana</v>
+      </c>
+      <c r="AT2" t="str">
         <v>Descanso</v>
       </c>
-      <c r="AO2" t="str">
-        <v/>
-      </c>
-      <c r="AP2" t="str">
-        <v/>
-      </c>
-      <c r="AQ2" t="str">
-        <v/>
-      </c>
-      <c r="AR2" t="str">
-        <v/>
-      </c>
-      <c r="AS2" t="str">
-        <v/>
-      </c>
-      <c r="AT2" t="str">
-        <v>Turno estándar Zona Norte</v>
+      <c r="AU2" t="str">
+        <v/>
+      </c>
+      <c r="AV2" t="str">
+        <v/>
+      </c>
+      <c r="AW2" t="str">
+        <v/>
+      </c>
+      <c r="AX2" t="str">
+        <v/>
+      </c>
+      <c r="AY2" t="str">
+        <v/>
+      </c>
+      <c r="AZ2" t="str">
+        <v>Descanso dominical programado</v>
+      </c>
+      <c r="BA2" t="str">
+        <v>Cumplir con EPP y dotación al día</v>
       </c>
     </row>
     <row r="3">
@@ -733,7 +782,7 @@
         <v>1020456789</v>
       </c>
       <c r="B3" t="str">
-        <v>Andres Felipe Restrepo</v>
+        <v>Andrés Felipe Restrepo</v>
       </c>
       <c r="C3" t="str">
         <v>2026-08-03</v>
@@ -742,7 +791,7 @@
         <v>Partido</v>
       </c>
       <c r="E3" t="str">
-        <v>Mercado Libre Colombia</v>
+        <v>Droguerías Comfandi</v>
       </c>
       <c r="F3" t="str">
         <v>08:00</v>
@@ -757,135 +806,157 @@
         <v>19:00</v>
       </c>
       <c r="J3" t="str">
+        <v>Entrega de medicamentos refrigerados</v>
+      </c>
+      <c r="K3" t="str">
         <v>Continua</v>
       </c>
-      <c r="K3" t="str">
-        <v>Mercado Libre Colombia</v>
-      </c>
       <c r="L3" t="str">
+        <v>Droguerías Comfandi</v>
+      </c>
+      <c r="M3" t="str">
         <v>07:00</v>
       </c>
-      <c r="M3" t="str">
+      <c r="N3" t="str">
         <v>15:00</v>
       </c>
-      <c r="N3" t="str">
-        <v/>
-      </c>
       <c r="O3" t="str">
         <v/>
       </c>
       <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v>Ruta centros comerciales sur</v>
+      </c>
+      <c r="R3" t="str">
         <v>Partido</v>
       </c>
-      <c r="Q3" t="str">
+      <c r="S3" t="str">
         <v>Almacenes Éxito S.A.</v>
       </c>
-      <c r="R3" t="str">
+      <c r="T3" t="str">
         <v>08:00</v>
       </c>
-      <c r="S3" t="str">
+      <c r="U3" t="str">
         <v>12:00</v>
       </c>
-      <c r="T3" t="str">
+      <c r="V3" t="str">
         <v>15:00</v>
       </c>
-      <c r="U3" t="str">
+      <c r="W3" t="str">
         <v>19:00</v>
       </c>
-      <c r="V3" t="str">
+      <c r="X3" t="str">
+        <v>Cobro contraentrega con datáfono</v>
+      </c>
+      <c r="Y3" t="str">
         <v>Continua</v>
       </c>
-      <c r="W3" t="str">
+      <c r="Z3" t="str">
         <v>Almacenes Éxito S.A.</v>
       </c>
-      <c r="X3" t="str">
+      <c r="AA3" t="str">
         <v>07:00</v>
       </c>
-      <c r="Y3" t="str">
+      <c r="AB3" t="str">
         <v>15:00</v>
       </c>
-      <c r="Z3" t="str">
-        <v/>
-      </c>
-      <c r="AA3" t="str">
-        <v/>
-      </c>
-      <c r="AB3" t="str">
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v>Apoyo en despacho sede central</v>
+      </c>
+      <c r="AF3" t="str">
         <v>Partido</v>
       </c>
-      <c r="AC3" t="str">
-        <v>Mercado Libre Colombia</v>
-      </c>
-      <c r="AD3" t="str">
+      <c r="AG3" t="str">
+        <v>Droguerías Comfandi</v>
+      </c>
+      <c r="AH3" t="str">
         <v>08:00</v>
       </c>
-      <c r="AE3" t="str">
+      <c r="AI3" t="str">
         <v>12:00</v>
       </c>
-      <c r="AF3" t="str">
+      <c r="AJ3" t="str">
         <v>15:00</v>
       </c>
-      <c r="AG3" t="str">
+      <c r="AK3" t="str">
         <v>19:00</v>
       </c>
-      <c r="AH3" t="str">
+      <c r="AL3" t="str">
+        <v>Verificar direcciones con cliente</v>
+      </c>
+      <c r="AM3" t="str">
         <v>Continua</v>
       </c>
-      <c r="AI3" t="str">
-        <v>Mercado Libre Colombia</v>
-      </c>
-      <c r="AJ3" t="str">
+      <c r="AN3" t="str">
+        <v>Droguerías Comfandi</v>
+      </c>
+      <c r="AO3" t="str">
         <v>08:00</v>
       </c>
-      <c r="AK3" t="str">
+      <c r="AP3" t="str">
         <v>14:00</v>
       </c>
-      <c r="AL3" t="str">
-        <v/>
-      </c>
-      <c r="AM3" t="str">
-        <v/>
-      </c>
-      <c r="AN3" t="str">
+      <c r="AQ3" t="str">
+        <v/>
+      </c>
+      <c r="AR3" t="str">
+        <v/>
+      </c>
+      <c r="AS3" t="str">
+        <v>Jornada continua fin de semana</v>
+      </c>
+      <c r="AT3" t="str">
         <v>Descanso</v>
       </c>
-      <c r="AO3" t="str">
-        <v/>
-      </c>
-      <c r="AP3" t="str">
-        <v/>
-      </c>
-      <c r="AQ3" t="str">
-        <v/>
-      </c>
-      <c r="AR3" t="str">
-        <v/>
-      </c>
-      <c r="AS3" t="str">
-        <v/>
-      </c>
-      <c r="AT3" t="str">
-        <v>Turno estándar Zona Sur</v>
+      <c r="AU3" t="str">
+        <v/>
+      </c>
+      <c r="AV3" t="str">
+        <v/>
+      </c>
+      <c r="AW3" t="str">
+        <v/>
+      </c>
+      <c r="AX3" t="str">
+        <v/>
+      </c>
+      <c r="AY3" t="str">
+        <v/>
+      </c>
+      <c r="AZ3" t="str">
+        <v>Descanso dominical programado</v>
+      </c>
+      <c r="BA3" t="str">
+        <v>Turno semanal zona sur</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AT3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:BA3"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F18"/>
   <cols>
     <col min="1" max="1" width="35.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>INSTRUCCIONES DE CARGA MASIVA DE TURNOS - SERGEM MENSAJERIA S.A.S.</v>
+        <v>INSTRUCCIONES PARA LA CARGA MASIVA DE TURNOS - SERGEM MENSAJERÍA S.A.S.</v>
       </c>
     </row>
     <row r="2">
@@ -895,7 +966,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>1. Tipos de Turno:</v>
+        <v>1. Tipos de Turno Válidos:</v>
       </c>
       <c r="B3" t="str">
         <v>Continua</v>
@@ -918,7 +989,7 @@
         <v>2. Formato de Horas:</v>
       </c>
       <c r="B4" t="str">
-        <v>HH:MM (ejemplo: 07:00, 15:00, 18:00)</v>
+        <v>HH:MM (Ej: 07:00, 15:00, 18:00)</v>
       </c>
     </row>
     <row r="5">
@@ -926,7 +997,7 @@
         <v>3. Turno Partido:</v>
       </c>
       <c r="B5" t="str">
-        <v>Diligencie HoraInicio1-HoraFin1 y HoraInicio2-HoraFin2</v>
+        <v>Diligenciar HoraInicio1 - HoraFin1 (mañana) y HoraInicio2 - HoraFin2 (tarde)</v>
       </c>
     </row>
     <row r="6">
@@ -934,7 +1005,7 @@
         <v>4. Turno Continuo:</v>
       </c>
       <c r="B6" t="str">
-        <v>Diligencie HoraInicio1 y HoraFin1</v>
+        <v>Diligenciar únicamente HoraInicio1 y HoraFin1</v>
       </c>
     </row>
     <row r="7">
@@ -942,47 +1013,103 @@
         <v>5. Descanso:</v>
       </c>
       <c r="B7" t="str">
-        <v>Escriba Descanso en la columna de Tipo.</v>
+        <v>Colocar "Descanso" en el campo Tipo. Los campos de hora y cliente pueden quedar vacíos.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v/>
+        <v>6. Columna de Observaciones / Recomendaciones en Cada Día:</v>
+      </c>
+      <c r="B8" t="str">
+        <v>Cada día incluye su columna "[Día]_Observaciones" para añadir recomendaciones específicas (ej: llegar antes, ruta express, llevar datáfono, sede asignada, etc.).</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>CLIENTES FRECUENTES DE SERGEM:</v>
+        <v xml:space="preserve">   Estas observaciones son visibles en tiempo real para el repartidor y el jefe de zona.</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Almacenes Éxito S.A.</v>
+        <v>7. Cédula del Repartidor:</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Si el repartidor ya existe en la plataforma, sus turnos se actualizarán automáticamente.</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Droguerías Comfandi</v>
+        <v xml:space="preserve">   Si la cédula es nueva, el sistema registrará al repartidor automáticamente en el equipo.</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Mercado Libre Colombia</v>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Postobón S.A.</v>
+        <v>LISTADO DE CLIENTES DISPONIBLES EN SERGEM:</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Nutresa Logistics</v>
+        <v>Código / ID</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Nombre del Cliente</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Ciudad / Sede</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>CLI-01</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Almacenes Éxito S.A.</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Cali</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>CLI-02</v>
+      </c>
+      <c r="B16" t="str">
+        <v>Droguerías Comfandi</v>
+      </c>
+      <c r="C16" t="str">
+        <v>Cali</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>CLI-03</v>
+      </c>
+      <c r="B17" t="str">
+        <v>Mercado Libre Colombia</v>
+      </c>
+      <c r="C17" t="str">
+        <v>Cali</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>CLI-04</v>
+      </c>
+      <c r="B18" t="str">
+        <v>Postobón S.A.</v>
+      </c>
+      <c r="C18" t="str">
+        <v>Cali</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
   </ignoredErrors>
 </worksheet>
 </file>